--- a/data/trans_orig/IP22C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22C-Edad-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26740</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31057</t>
+          <t>31044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25336</t>
+          <t>25604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31136</t>
+          <t>31407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54415</t>
+          <t>54462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61323</t>
+          <t>61262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42525</t>
+          <t>42473</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48605</t>
+          <t>48601</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61134</t>
+          <t>60888</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65676</t>
+          <t>65679</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>106612</t>
+          <t>106722</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>113617</t>
+          <t>113951</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>15364</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33543</t>
+          <t>33452</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>21638</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>25747</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31900</t>
+          <t>31300</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>48933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56528</t>
+          <t>56237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>114183</t>
+          <t>114541</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>122533</t>
+          <t>122677</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135007</t>
+          <t>134622</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>145086</t>
+          <t>144948</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>252111</t>
+          <t>252863</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>265067</t>
+          <t>265583</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>21213</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39607</t>
+          <t>39929</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45700</t>
+          <t>45722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30158</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36817</t>
+          <t>36761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72299</t>
+          <t>73000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81209</t>
+          <t>81804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61219</t>
+          <t>60131</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68279</t>
+          <t>68418</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82869</t>
+          <t>82543</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91585</t>
+          <t>91600</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>146949</t>
+          <t>145680</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157850</t>
+          <t>157933</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26002</t>
+          <t>26024</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40975</t>
+          <t>40410</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46222</t>
+          <t>46193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37258</t>
+          <t>37324</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54249</t>
+          <t>54251</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58539</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>139332</t>
+          <t>139443</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>149934</t>
+          <t>149415</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>180640</t>
+          <t>180717</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>192555</t>
+          <t>192807</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>324109</t>
+          <t>323174</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>340040</t>
+          <t>340153</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21886</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>34255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>559</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20599</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25579</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20605</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36612</t>
+          <t>36775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45320</t>
+          <t>45009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37241</t>
+          <t>37939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42622</t>
+          <t>42764</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>28375</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34768</t>
+          <t>35036</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>68718</t>
+          <t>68627</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>76488</t>
+          <t>76873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>20969</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26780</t>
+          <t>26811</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>22384</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45592</t>
+          <t>44920</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52444</t>
+          <t>52521</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7089</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17887</t>
+          <t>17711</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>23606</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32718</t>
+          <t>33237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40550</t>
+          <t>40554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>99191</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>109309</t>
+          <t>109689</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>90401</t>
+          <t>90483</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101999</t>
+          <t>102156</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>193632</t>
+          <t>193585</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>209572</t>
+          <t>208802</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>24999</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>22995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27071</t>
+          <t>27064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>379</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>506</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20954</t>
+          <t>20991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28185</t>
+          <t>28165</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39220</t>
+          <t>39224</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47391</t>
+          <t>47316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>556</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21903</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>26508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45278</t>
+          <t>45563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53618</t>
+          <t>53486</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34572</t>
+          <t>33000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28124</t>
+          <t>28045</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36035</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64786</t>
+          <t>65121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72950</t>
+          <t>73162</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83094</t>
+          <t>82879</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92466</t>
+          <t>92389</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95364</t>
+          <t>94476</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106112</t>
+          <t>106010</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>182002</t>
+          <t>181580</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>196902</t>
+          <t>196510</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP22C-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28910</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25322</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30937</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>29780</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26997</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>31044</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>26764</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31052</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,07%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28910</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25604</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31407</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,04%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54462</t>
+          <t>54635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61262</t>
+          <t>61330</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3199</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6787</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>21,14%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1876</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4659</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4892</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,93%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,72%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3199</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32109</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>32109</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32109</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>31656</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>31656</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>31656</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>32109</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>32109</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>32109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,107 +1179,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>778</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3160</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3817</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3246</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>64308</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>61125</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>65679</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>92,23%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>46503</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>42473</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>48601</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>42671</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>49132</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>93,19%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>85,11%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>64308</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>60888</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>65679</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>106722</t>
+          <t>105897</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>113951</t>
+          <t>113616</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -1405,92 +1405,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5153</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2620</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6014</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6471</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,25%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>4590</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>1970</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5390</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66278</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66278</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>66278</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>49902</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>49902</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>49902</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>66278</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>66278</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>66278</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1748,74 +1748,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18065</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14893</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18738</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>79,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18573</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16154</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16220</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>19149</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>96,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>84,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18065</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15364</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18738</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>96,41%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>81,99%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>55</t>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>33947</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1866,102 +1866,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3845</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>576</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2995</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2929</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3374</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3941</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1249</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4436</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>18738</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>18738</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>18738</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>19149</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>19149</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>19149</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>18738</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>18738</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>18738</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,107 +2091,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4750</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1358</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4103</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4630</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>12,33%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5025</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -2204,74 +2204,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29263</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25346</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31339</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>24292</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>21638</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>21485</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>25487</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,31%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>84,9%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>84,3%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>29263</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>25747</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>31300</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,97%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>77,4%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>80</t>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48933</t>
+          <t>49164</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56237</t>
+          <t>56252</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5984</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>17,99%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>1195</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3849</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,69%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2644</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5978</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>33265</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>33265</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>33265</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>25487</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>25487</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>25487</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>33265</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>33265</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>33265</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2547,72 +2547,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4786</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>778</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4655</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3663</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4735</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -2660,72 +2660,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>140545</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>135232</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>144965</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>93,45%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>119149</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>114541</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>122677</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>114370</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>122457</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>94,42%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>140545</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>134622</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>144948</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>93,45%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>252863</t>
+          <t>252379</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>265583</t>
+          <t>265372</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -2773,72 +2773,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8486</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4663</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13694</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>6268</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2915</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10609</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>10830</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>4,97%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>8486</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>4469</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>13893</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -2886,57 +2886,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>150389</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>150389</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>150389</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>126195</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>126195</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>126195</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>150389</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>150389</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>150389</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3067,7 +3067,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3348,72 +3348,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34212</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30080</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36808</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,6%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43634</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>39929</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45722</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>39581</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>45726</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>92,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>34212</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>30163</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>36761</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,26%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73000</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81804</t>
+          <t>81769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -3461,72 +3461,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4551</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8683</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3397</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7102</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7450</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,22%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4551</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8600</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -3574,57 +3574,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38763</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>38763</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38763</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>47031</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>47031</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>47031</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>38763</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>38763</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>38763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3804,74 +3804,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>88059</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82810</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91594</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>86,66%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>65455</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>60131</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>68418</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>60958</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>68416</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>93,4%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>85,81%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>86,98%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>97,63%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>88059</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>82543</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>91600</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>92,15%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>86,38%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>95,86%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>145680</t>
+          <t>147495</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157933</t>
+          <t>158529</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -3917,72 +3917,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7497</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12746</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4624</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1661</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9948</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1663</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,6%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7497</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3956</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13013</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -4030,57 +4030,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>95556</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95556</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>95556</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>70079</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>70079</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>70079</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>95556</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>95556</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>95556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4260,74 +4260,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24686</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21852</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26008</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>92,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>82,06%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>97,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19622</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17106</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16911</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>20231</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>96,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>84,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>83,59%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24686</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>21236</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>26024</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>79,74%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>62</t>
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40410</t>
+          <t>40864</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46193</t>
+          <t>46200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -4373,72 +4373,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4779</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3125</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5395</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -4486,57 +4486,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26631</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26631</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26631</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>20231</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>20231</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>20231</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>26631</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>26631</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>26631</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4716,74 +4716,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>40362</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>37136</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>41576</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>16953</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>14502</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13871</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>17562</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>82,57%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>78,98%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>40362</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>37324</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>41576</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>85</t>
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54251</t>
+          <t>54224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58544</t>
+          <t>58543</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -4829,72 +4829,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,68%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3060</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>17,43%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>4252</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -4942,57 +4942,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>41576</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>41576</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>41576</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>17562</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>17562</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>17562</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>41576</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>41576</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>41576</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5172,72 +5172,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>187320</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>180590</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>192767</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>92,49%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>89,17%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>145664</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>139443</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>149415</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>139157</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>149578</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>94,04%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>187320</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>180717</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>192807</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>92,49%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>323174</t>
+          <t>324787</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>340153</t>
+          <t>339929</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -5285,72 +5285,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15206</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9759</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>21936</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>9239</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>5488</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>15460</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>5325</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>15746</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>5,96%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>15206</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>9719</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>21809</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34255</t>
+          <t>32642</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -5398,57 +5398,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>202526</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>202526</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>202526</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>154903</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>154903</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>154903</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>202526</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>202526</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>202526</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5568,7 +5568,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5579,7 +5579,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5747,72 +5747,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1743</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5463</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5677</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>7,69%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1743</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5746</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -5860,72 +5860,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17784</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14027</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20459</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>62,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,15%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>23582</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20158</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25575</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>20047</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25353</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,01%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17784</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13875</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20674</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>79,23%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>36312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45009</t>
+          <t>44870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -5973,72 +5973,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2918</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6591</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>29,36%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>604</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3434</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3334</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2918</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6385</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -6086,57 +6086,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22445</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22445</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22445</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>26199</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>26199</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>26199</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>22445</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>22445</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22445</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6203,72 +6203,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1592</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3953</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4244</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>3,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>468</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -6316,72 +6316,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>32386</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28312</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>35066</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>88,66%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>77,5%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>96,0%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41032</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>37939</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>42764</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>38182</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>42814</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>94,65%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>32386</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>28375</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>35036</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>88,66%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>68627</t>
+          <t>68508</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>76873</t>
+          <t>76333</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -6429,72 +6429,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4143</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8217</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>727</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3628</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3889</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4143</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1493</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8154</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -6542,57 +6542,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36529</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>36529</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36529</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>43351</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>43351</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>43351</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>36529</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>36529</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>36529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6659,107 +6659,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3169</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3714</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -6772,72 +6772,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25317</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22460</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26722</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>94,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>84,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>24404</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20969</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26811</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20734</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26420</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>86,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>74,59%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>95,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>25317</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>22384</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>26722</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44920</t>
+          <t>45392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52521</t>
+          <t>52433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -6885,72 +6885,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3981</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3708</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7143</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1692</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7378</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>13,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>25,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -6998,57 +6998,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26722</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26722</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26722</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>28112</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>28112</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>28112</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>26722</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>26722</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>26722</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7115,107 +7115,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>644</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3225</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2775</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,52%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3277</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4100</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -7228,72 +7228,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21406</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17556</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23575</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>70,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>16170</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13013</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17690</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12995</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>17692</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>88,33%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>71,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>21406</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>17711</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>23606</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>85,58%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>33340</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>40582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -7341,72 +7341,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3608</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7458</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>29,82%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>1492</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4541</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4595</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,15%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3608</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7303</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -7454,57 +7454,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>25014</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>25014</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>25014</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>18306</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>18306</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>18306</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>25014</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>25014</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>25014</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7571,72 +7571,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7461</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>4250</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8205</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8341</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7361</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -7684,72 +7684,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>96894</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>89766</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>101783</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>81,08%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>91,94%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>105187</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>99877</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>109689</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>99708</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>109629</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>90,7%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>86,12%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>96894</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>90483</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>102156</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>193585</t>
+          <t>193205</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>208802</t>
+          <t>208934</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -7797,72 +7797,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11395</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7020</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17946</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>6531</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3265</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11257</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>11392</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>5,63%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>11395</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>6774</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>17562</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24999</t>
+          <t>26359</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -7910,57 +7910,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>110711</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>110711</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>110711</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>115968</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>115968</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>115968</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>110711</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>110711</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>110711</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8091,7 +8091,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8372,74 +8372,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9544</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10198</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13809</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11174</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14624</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>94,42%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12354</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9330</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>13044</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>71,53%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12028</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10124</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12819</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,83%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>78,98%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>46</t>
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22995</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27064</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -8485,72 +8485,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2321</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>22,76%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3714</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,59%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>791</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>309</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -8598,57 +8598,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10198</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10198</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10198</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14624</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14624</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14624</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8715,72 +8715,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3624</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15,1%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3132</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6007</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,22 +8790,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>425</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -8828,72 +8828,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21400</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>18067</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>23050</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>89,17%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>75,28%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>18671</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>15562</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>20204</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>89,08%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>74,24%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25540</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20991</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28165</t>
+          <t>17402</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>44211</t>
+          <t>37323</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39224</t>
+          <t>33247</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>47316</t>
+          <t>39638</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -8941,72 +8941,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4570</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1798</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -9054,57 +9054,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23999</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23999</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23999</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20961</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20961</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20961</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9171,107 +9171,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3386</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4486</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>19,03%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>4437</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>4843</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -9284,74 +9284,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28858</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25349</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30553</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>82,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19572</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15514</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21897</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>83,68%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>19645</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15517</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>22073</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>83,32%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>65,81%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>93,62%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>30655</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26508</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>32583</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>81,36%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>62</t>
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>50227</t>
+          <t>48503</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45563</t>
+          <t>43825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53486</t>
+          <t>51601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -9397,72 +9397,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1695</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5204</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2998</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>797</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>28,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,17 +9472,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -9510,57 +9510,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30553</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30553</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30553</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>23390</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>23390</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>23390</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32583</t>
+          <t>23578</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32583</t>
+          <t>23578</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32583</t>
+          <t>23578</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>55972</t>
+          <t>54131</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>55972</t>
+          <t>54131</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>55972</t>
+          <t>54131</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9740,74 +9740,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>32862</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28348</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>35356</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>36802</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>33000</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>37424</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,18%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>33400</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>30457</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>34011</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>89,55%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>33463</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>28045</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>35898</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,35%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>75,72%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>84</t>
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>70264</t>
+          <t>66262</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65121</t>
+          <t>61134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73162</t>
+          <t>68899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -9853,72 +9853,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7936</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>21,87%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4424</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3554</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,82%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3576</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>8994</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -9966,57 +9966,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>36284</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>36284</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>36284</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>37424</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>37424</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>37424</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37039</t>
+          <t>34011</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37039</t>
+          <t>34011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37039</t>
+          <t>34011</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>70295</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>70295</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>70295</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88853</t>
+          <t>92664</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82879</t>
+          <t>86230</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92389</t>
+          <t>96386</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>101687</t>
+          <t>81324</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94476</t>
+          <t>75708</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106010</t>
+          <t>84839</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>190540</t>
+          <t>173987</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>181580</t>
+          <t>166324</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>196510</t>
+          <t>180012</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14192</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8997</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>96398</t>
+          <t>101034</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96398</t>
+          <t>101034</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>96398</t>
+          <t>101034</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
